--- a/evaluations/response_time_increasing_clients/direct_client/aggregated_workload.xlsx
+++ b/evaluations/response_time_increasing_clients/direct_client/aggregated_workload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\evaluations\response_time_increasing_clients\direct_client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D425891-29C8-462F-88CB-1749269271F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD6A657-05BD-4C9B-9B0B-AB4743417519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,6 +63,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -150,7 +151,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1"/>
